--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6051,0.0632,0.0232,0.3596</t>
-  </si>
-  <si>
-    <t>0.0133,0.0348,0.0013,0.9906</t>
-  </si>
-  <si>
-    <t>0.6628,0.0269,0.0086,0.3485</t>
-  </si>
-  <si>
-    <t>0.2629,0.0112,0.0139,0.8532</t>
-  </si>
-  <si>
-    <t>0.9866,0.0083,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9889,0.0044,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9610,0.0275,0.0080,0.0031</t>
-  </si>
-  <si>
-    <t>0.9896,0.0031,0.0007,0.0019</t>
-  </si>
-  <si>
-    <t>0.9676,0.0264,0.0059,0.0021</t>
-  </si>
-  <si>
-    <t>0.9672,0.0204,0.0015,0.0032</t>
-  </si>
-  <si>
-    <t>0.9804,0.0097,0.0013,0.0024</t>
-  </si>
-  <si>
-    <t>0.9879,0.0052,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.4043,0.1272,0.5403,0.0270</t>
-  </si>
-  <si>
-    <t>0.0751,0.0177,0.9261,0.0115</t>
-  </si>
-  <si>
-    <t>0.3200,0.0190,0.8016,0.0105</t>
-  </si>
-  <si>
-    <t>0.3989,0.0579,0.6451,0.0153</t>
-  </si>
-  <si>
-    <t>0.5032,0.0693,0.5528,0.0166</t>
-  </si>
-  <si>
-    <t>0.0524,0.9567,0.0050,0.0004</t>
-  </si>
-  <si>
-    <t>0.2757,0.8254,0.0128,0.0011</t>
-  </si>
-  <si>
-    <t>0.4133,0.6760,0.0156,0.0020</t>
-  </si>
-  <si>
-    <t>0.1458,0.8817,0.0120,0.0017</t>
-  </si>
-  <si>
-    <t>0.0174,0.9810,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.4828,0.0666,0.3379,0.2287</t>
-  </si>
-  <si>
-    <t>0.3303,0.0804,0.6044,0.0995</t>
-  </si>
-  <si>
-    <t>0.0105,0.0108,0.9679,0.0082</t>
-  </si>
-  <si>
-    <t>0.1211,0.0154,0.8806,0.0095</t>
-  </si>
-  <si>
-    <t>0.0155,0.0016,0.9870,0.0012</t>
-  </si>
-  <si>
-    <t>0.0353,0.0092,0.9565,0.0071</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9956,0.0118</t>
-  </si>
-  <si>
-    <t>0.5410,0.5793,0.0171,0.0059</t>
-  </si>
-  <si>
-    <t>0.6612,0.1116,0.3380,0.0157</t>
-  </si>
-  <si>
-    <t>0.0035,0.0591,0.9862,0.0010</t>
-  </si>
-  <si>
-    <t>0.0111,0.8537,0.4507,0.0006</t>
-  </si>
-  <si>
-    <t>0.7199,0.2740,0.0380,0.0183</t>
-  </si>
-  <si>
-    <t>0.2352,0.7627,0.0762,0.0166</t>
-  </si>
-  <si>
-    <t>0.5795,0.5232,0.0194,0.0023</t>
-  </si>
-  <si>
-    <t>0.1138,0.8216,0.1766,0.0326</t>
-  </si>
-  <si>
-    <t>0.0011,0.9533,0.1179,0.0369</t>
-  </si>
-  <si>
-    <t>0.0180,0.0064,0.9642,0.0157</t>
-  </si>
-  <si>
-    <t>0.0048,0.4403,0.9081,0.0014</t>
-  </si>
-  <si>
-    <t>0.0621,0.0705,0.8609,0.0158</t>
-  </si>
-  <si>
-    <t>0.0300,0.6038,0.5886,0.0060</t>
-  </si>
-  <si>
-    <t>0.0019,0.9827,0.0601,0.0003</t>
-  </si>
-  <si>
-    <t>0.0777,0.4300,0.5853,0.0559</t>
-  </si>
-  <si>
-    <t>0.1935,0.5605,0.0878,0.4554</t>
-  </si>
-  <si>
-    <t>0.0036,0.9685,0.0351,0.0252</t>
-  </si>
-  <si>
-    <t>0.0027,0.9786,0.0766,0.0030</t>
-  </si>
-  <si>
-    <t>0.0004,0.9932,0.0272,0.0008</t>
-  </si>
-  <si>
-    <t>0.0057,0.6696,0.9088,0.0040</t>
-  </si>
-  <si>
-    <t>0.0022,0.3104,0.9708,0.0004</t>
-  </si>
-  <si>
-    <t>0.0725,0.0115,0.9109,0.0296</t>
-  </si>
-  <si>
-    <t>0.0060,0.0023,0.9900,0.0014</t>
-  </si>
-  <si>
-    <t>0.0062,0.1877,0.9513,0.0091</t>
-  </si>
-  <si>
-    <t>0.0112,0.0514,0.9607,0.0017</t>
-  </si>
-  <si>
-    <t>0.9380,0.0353,0.0013,0.0072</t>
-  </si>
-  <si>
-    <t>0.9531,0.0118,0.0016,0.0148</t>
-  </si>
-  <si>
-    <t>0.9185,0.0591,0.0264,0.0062</t>
-  </si>
-  <si>
-    <t>0.0110,0.0343,0.9813,0.0038</t>
-  </si>
-  <si>
-    <t>0.9559,0.0450,0.0026,0.0020</t>
-  </si>
-  <si>
-    <t>0.9875,0.0036,0.0007,0.0022</t>
-  </si>
-  <si>
-    <t>0.9643,0.0272,0.0058,0.0020</t>
-  </si>
-  <si>
-    <t>0.0011,0.8706,0.9258,0.0004</t>
-  </si>
-  <si>
-    <t>0.0027,0.3321,0.9729,0.0011</t>
-  </si>
-  <si>
-    <t>0.0051,0.0293,0.9574,0.0210</t>
-  </si>
-  <si>
-    <t>0.0029,0.8138,0.8841,0.0010</t>
-  </si>
-  <si>
-    <t>0.0010,0.0497,0.9899,0.0018</t>
-  </si>
-  <si>
-    <t>0.0439,0.8708,0.2448,0.0016</t>
-  </si>
-  <si>
-    <t>0.0408,0.9611,0.0081,0.0006</t>
-  </si>
-  <si>
-    <t>0.6784,0.0674,0.3858,0.0061</t>
-  </si>
-  <si>
-    <t>0.2826,0.1128,0.7153,0.0118</t>
-  </si>
-  <si>
-    <t>0.0046,0.1640,0.9839,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.9074,0.6180,0.0004</t>
-  </si>
-  <si>
-    <t>0.0024,0.8751,0.7341,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.9627,0.5538,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.9739,0.6369,0.0002</t>
-  </si>
-  <si>
-    <t>0.1500,0.0099,0.2408,0.6749</t>
-  </si>
-  <si>
-    <t>0.0020,0.0864,0.0013,0.9956</t>
-  </si>
-  <si>
-    <t>0.0208,0.0005,0.0039,0.9873</t>
-  </si>
-  <si>
-    <t>0.0941,0.0088,0.0026,0.9625</t>
-  </si>
-  <si>
-    <t>0.0178,0.0180,0.0076,0.9849</t>
-  </si>
-  <si>
-    <t>0.0232,0.0082,0.0039,0.9868</t>
-  </si>
-  <si>
-    <t>0.0007,0.9664,0.7019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.7809,0.9333,0.0004</t>
-  </si>
-  <si>
-    <t>0.0025,0.7949,0.8195,0.0004</t>
-  </si>
-  <si>
-    <t>0.0038,0.8479,0.6855,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.9759,0.5770,0.0000</t>
-  </si>
-  <si>
-    <t>0.0060,0.8230,0.7090,0.0022</t>
-  </si>
-  <si>
-    <t>0.9900,0.0063,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9793,0.0133,0.0023,0.0015</t>
-  </si>
-  <si>
-    <t>0.9346,0.0874,0.0051,0.0010</t>
-  </si>
-  <si>
-    <t>0.9784,0.0073,0.0011,0.0035</t>
-  </si>
-  <si>
-    <t>0.9678,0.0223,0.0011,0.0025</t>
-  </si>
-  <si>
-    <t>0.9861,0.0080,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.9750,0.0179,0.0018,0.0017</t>
-  </si>
-  <si>
-    <t>0.9721,0.0219,0.0019,0.0020</t>
-  </si>
-  <si>
-    <t>0.9923,0.0016,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9913,0.0055,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9907,0.0022,0.0003,0.0020</t>
-  </si>
-  <si>
-    <t>0.9883,0.0077,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9858,0.0069,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.9795,0.0105,0.0013,0.0025</t>
-  </si>
-  <si>
-    <t>0.9863,0.0097,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.9895,0.0057,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.0038,0.0355,0.9842,0.0032</t>
-  </si>
-  <si>
-    <t>0.0674,0.0581,0.8592,0.0098</t>
-  </si>
-  <si>
-    <t>0.6181,0.0102,0.1483,0.1758</t>
-  </si>
-  <si>
-    <t>0.0971,0.0196,0.9001,0.0141</t>
-  </si>
-  <si>
-    <t>0.1695,0.8475,0.0142,0.0014</t>
-  </si>
-  <si>
-    <t>0.1195,0.8888,0.0186,0.0017</t>
-  </si>
-  <si>
-    <t>0.2182,0.8047,0.0045,0.0074</t>
-  </si>
-  <si>
-    <t>0.3586,0.7278,0.0031,0.0048</t>
-  </si>
-  <si>
-    <t>0.1435,0.8958,0.0051,0.0013</t>
-  </si>
-  <si>
-    <t>0.0501,0.9514,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.6691,0.4020,0.0183,0.0052</t>
-  </si>
-  <si>
-    <t>0.4813,0.1536,0.4628,0.0188</t>
-  </si>
-  <si>
-    <t>0.1936,0.0480,0.7948,0.0154</t>
-  </si>
-  <si>
-    <t>0.5339,0.0364,0.3846,0.1035</t>
-  </si>
-  <si>
-    <t>0.3960,0.1322,0.5730,0.0277</t>
-  </si>
-  <si>
-    <t>0.3775,0.2500,0.2791,0.4126</t>
-  </si>
-  <si>
-    <t>0.0028,0.9832,0.0096,0.0093</t>
-  </si>
-  <si>
-    <t>0.0023,0.9874,0.0167,0.0022</t>
-  </si>
-  <si>
-    <t>0.0636,0.7898,0.3475,0.0416</t>
-  </si>
-  <si>
-    <t>0.0007,0.9790,0.7090,0.0002</t>
-  </si>
-  <si>
-    <t>0.0723,0.9412,0.0169,0.0002</t>
-  </si>
-  <si>
-    <t>0.3932,0.6878,0.0208,0.0010</t>
-  </si>
-  <si>
-    <t>0.5062,0.5964,0.0217,0.0012</t>
-  </si>
-  <si>
-    <t>0.9503,0.0407,0.0031,0.0043</t>
-  </si>
-  <si>
-    <t>0.9687,0.0145,0.0025,0.0048</t>
-  </si>
-  <si>
-    <t>0.9852,0.0034,0.0005,0.0041</t>
-  </si>
-  <si>
-    <t>0.9699,0.0045,0.0015,0.0134</t>
-  </si>
-  <si>
-    <t>0.9776,0.0155,0.0017,0.0017</t>
-  </si>
-  <si>
-    <t>0.8974,0.0375,0.0963,0.0056</t>
-  </si>
-  <si>
-    <t>0.9775,0.0063,0.0007,0.0046</t>
-  </si>
-  <si>
-    <t>0.9627,0.0243,0.0050,0.0030</t>
-  </si>
-  <si>
-    <t>0.0017,0.7960,0.8851,0.0004</t>
-  </si>
-  <si>
-    <t>0.0039,0.7654,0.8348,0.0006</t>
-  </si>
-  <si>
-    <t>0.0056,0.5028,0.8623,0.0006</t>
-  </si>
-  <si>
-    <t>0.0297,0.5639,0.6021,0.0074</t>
-  </si>
-  <si>
-    <t>0.4493,0.3915,0.0907,0.1911</t>
-  </si>
-  <si>
-    <t>0.4986,0.1546,0.4838,0.0634</t>
-  </si>
-  <si>
-    <t>0.0725,0.0092,0.9326,0.0167</t>
-  </si>
-  <si>
-    <t>0.4675,0.1162,0.5193,0.0148</t>
-  </si>
-  <si>
-    <t>0.1377,0.0144,0.0020,0.9370</t>
-  </si>
-  <si>
-    <t>0.0006,0.0015,0.0006,0.9993</t>
-  </si>
-  <si>
-    <t>0.0177,0.0574,0.0088,0.9810</t>
-  </si>
-  <si>
-    <t>0.0340,0.0068,0.0010,0.9877</t>
-  </si>
-  <si>
-    <t>0.0004,0.9543,0.8598,0.0002</t>
-  </si>
-  <si>
-    <t>0.9594,0.0413,0.0014,0.0019</t>
-  </si>
-  <si>
-    <t>0.3921,0.6069,0.0060,0.0299</t>
-  </si>
-  <si>
-    <t>0.9511,0.0136,0.0039,0.0161</t>
-  </si>
-  <si>
-    <t>0.9323,0.0657,0.0028,0.0050</t>
-  </si>
-  <si>
-    <t>0.9305,0.0091,0.0035,0.0387</t>
-  </si>
-  <si>
-    <t>0.2138,0.0389,0.0300,0.8612</t>
-  </si>
-  <si>
-    <t>0.9494,0.0134,0.0097,0.0149</t>
-  </si>
-  <si>
-    <t>0.0053,0.4650,0.9186,0.0074</t>
-  </si>
-  <si>
-    <t>0.7883,0.0027,0.0321,0.1379</t>
-  </si>
-  <si>
-    <t>0.8578,0.0022,0.0067,0.1454</t>
-  </si>
-  <si>
-    <t>0.2891,0.7260,0.0458,0.0192</t>
-  </si>
-  <si>
-    <t>0.6226,0.4370,0.0203,0.0133</t>
-  </si>
-  <si>
-    <t>0.8382,0.1153,0.0640,0.0068</t>
-  </si>
-  <si>
-    <t>0.6886,0.2432,0.0986,0.0166</t>
-  </si>
-  <si>
-    <t>0.6148,0.4105,0.0513,0.0160</t>
-  </si>
-  <si>
-    <t>0.6808,0.3546,0.0345,0.0104</t>
-  </si>
-  <si>
-    <t>0.9694,0.0155,0.0042,0.0038</t>
-  </si>
-  <si>
-    <t>0.9485,0.0158,0.0025,0.0136</t>
-  </si>
-  <si>
-    <t>0.9773,0.0083,0.0014,0.0037</t>
-  </si>
-  <si>
-    <t>0.9683,0.0065,0.0044,0.0099</t>
-  </si>
-  <si>
-    <t>0.9789,0.0024,0.0004,0.0097</t>
-  </si>
-  <si>
-    <t>0.9361,0.0442,0.0113,0.0052</t>
-  </si>
-  <si>
-    <t>0.9666,0.0125,0.0037,0.0063</t>
-  </si>
-  <si>
-    <t>0.9819,0.0067,0.0009,0.0029</t>
-  </si>
-  <si>
-    <t>0.1946,0.8693,0.0044,0.0010</t>
-  </si>
-  <si>
-    <t>0.5656,0.4601,0.0364,0.0010</t>
-  </si>
-  <si>
-    <t>0.3285,0.7495,0.0114,0.0016</t>
-  </si>
-  <si>
-    <t>0.5427,0.2168,0.3069,0.0075</t>
-  </si>
-  <si>
-    <t>0.8961,0.1141,0.0043,0.0047</t>
-  </si>
-  <si>
-    <t>0.8301,0.1756,0.0109,0.0101</t>
-  </si>
-  <si>
-    <t>0.9237,0.0602,0.0054,0.0073</t>
-  </si>
-  <si>
-    <t>0.7967,0.1590,0.0478,0.0213</t>
-  </si>
-  <si>
-    <t>0.0296,0.0341,0.9699,0.0030</t>
-  </si>
-  <si>
-    <t>0.9478,0.0262,0.0131,0.0060</t>
-  </si>
-  <si>
-    <t>0.0061,0.0080,0.9715,0.0261</t>
-  </si>
-  <si>
-    <t>0.0139,0.5180,0.8413,0.0132</t>
-  </si>
-  <si>
-    <t>0.0573,0.0201,0.9230,0.0170</t>
-  </si>
-  <si>
-    <t>0.0068,0.5333,0.9189,0.0020</t>
-  </si>
-  <si>
-    <t>0.0188,0.1123,0.9183,0.0066</t>
-  </si>
-  <si>
-    <t>0.0076,0.0024,0.9909,0.0013</t>
-  </si>
-  <si>
-    <t>0.0025,0.0125,0.9913,0.0019</t>
-  </si>
-  <si>
-    <t>0.2664,0.1185,0.6884,0.0475</t>
-  </si>
-  <si>
-    <t>0.2209,0.0704,0.7406,0.0116</t>
-  </si>
-  <si>
-    <t>0.4175,0.0896,0.5855,0.0244</t>
-  </si>
-  <si>
-    <t>0.2469,0.0741,0.7123,0.0079</t>
-  </si>
-  <si>
-    <t>0.1580,0.1762,0.7113,0.0072</t>
-  </si>
-  <si>
-    <t>0.2949,0.3629,0.4071,0.0355</t>
-  </si>
-  <si>
-    <t>0.5223,0.1004,0.4825,0.0411</t>
-  </si>
-  <si>
-    <t>0.2221,0.0466,0.7578,0.0167</t>
-  </si>
-  <si>
-    <t>0.7316,0.3349,0.0151,0.0025</t>
-  </si>
-  <si>
-    <t>0.7259,0.3905,0.0090,0.0022</t>
-  </si>
-  <si>
-    <t>0.8867,0.1559,0.0097,0.0010</t>
-  </si>
-  <si>
-    <t>0.9397,0.0411,0.0060,0.0071</t>
-  </si>
-  <si>
-    <t>0.8946,0.1689,0.0059,0.0008</t>
-  </si>
-  <si>
-    <t>0.2041,0.5494,0.1394,0.3933</t>
-  </si>
-  <si>
-    <t>0.7262,0.0488,0.2113,0.0589</t>
-  </si>
-  <si>
-    <t>0.5610,0.0961,0.1286,0.2127</t>
-  </si>
-  <si>
-    <t>0.2235,0.0374,0.7752,0.0181</t>
-  </si>
-  <si>
-    <t>0.4982,0.0585,0.5622,0.0114</t>
-  </si>
-  <si>
-    <t>0.0740,0.0415,0.8928,0.0265</t>
-  </si>
-  <si>
-    <t>0.0034,0.8937,0.4174,0.0056</t>
-  </si>
-  <si>
-    <t>0.0052,0.3835,0.8908,0.0011</t>
-  </si>
-  <si>
-    <t>0.0278,0.0494,0.9391,0.0071</t>
-  </si>
-  <si>
-    <t>0.0034,0.2964,0.9289,0.0020</t>
-  </si>
-  <si>
-    <t>0.9723,0.0173,0.0011,0.0026</t>
-  </si>
-  <si>
-    <t>0.9816,0.0077,0.0012,0.0022</t>
-  </si>
-  <si>
-    <t>0.9708,0.0102,0.0013,0.0058</t>
-  </si>
-  <si>
-    <t>0.9624,0.0311,0.0047,0.0021</t>
-  </si>
-  <si>
-    <t>0.9683,0.0213,0.0031,0.0031</t>
-  </si>
-  <si>
-    <t>0.9854,0.0087,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9813,0.0087,0.0009,0.0022</t>
-  </si>
-  <si>
-    <t>0.9798,0.0082,0.0017,0.0033</t>
-  </si>
-  <si>
-    <t>0.1630,0.0225,0.8760,0.0110</t>
-  </si>
-  <si>
-    <t>0.4393,0.0491,0.6544,0.0111</t>
-  </si>
-  <si>
-    <t>0.7897,0.1050,0.1435,0.0359</t>
-  </si>
-  <si>
-    <t>0.0353,0.1822,0.8333,0.0047</t>
-  </si>
-  <si>
-    <t>0.0003,0.0775,0.9922,0.0004</t>
-  </si>
-  <si>
-    <t>0.0150,0.0721,0.9344,0.0032</t>
-  </si>
-  <si>
-    <t>0.0018,0.0095,0.9937,0.0011</t>
-  </si>
-  <si>
-    <t>0.0840,0.1832,0.7378,0.0183</t>
-  </si>
-  <si>
-    <t>0.0019,0.0556,0.9855,0.0010</t>
-  </si>
-  <si>
-    <t>0.0066,0.0071,0.9750,0.0139</t>
-  </si>
-  <si>
-    <t>0.0430,0.1682,0.8213,0.0059</t>
-  </si>
-  <si>
-    <t>0.4065,0.0280,0.6004,0.0796</t>
-  </si>
-  <si>
-    <t>0.6141,0.0101,0.3997,0.0431</t>
-  </si>
-  <si>
-    <t>0.6803,0.0225,0.3407,0.0311</t>
-  </si>
-  <si>
-    <t>0.9757,0.0171,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9835,0.0102,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9716,0.0205,0.0057,0.0022</t>
-  </si>
-  <si>
-    <t>0.9682,0.0176,0.0028,0.0037</t>
-  </si>
-  <si>
-    <t>0.9681,0.0061,0.0012,0.0113</t>
-  </si>
-  <si>
-    <t>0.9798,0.0183,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.9746,0.0160,0.0031,0.0019</t>
-  </si>
-  <si>
-    <t>0.9583,0.0417,0.0035,0.0014</t>
-  </si>
-  <si>
-    <t>0.0312,0.2975,0.8160,0.0068</t>
-  </si>
-  <si>
-    <t>0.0068,0.1073,0.9555,0.0013</t>
-  </si>
-  <si>
-    <t>0.0013,0.0232,0.9883,0.0027</t>
-  </si>
-  <si>
-    <t>0.0330,0.3446,0.6634,0.0072</t>
-  </si>
-  <si>
-    <t>0.0123,0.0133,0.9646,0.0118</t>
-  </si>
-  <si>
-    <t>0.0426,0.0602,0.8596,0.1339</t>
-  </si>
-  <si>
-    <t>0.0797,0.2978,0.7306,0.0405</t>
-  </si>
-  <si>
-    <t>0.0052,0.1783,0.8767,0.0186</t>
-  </si>
-  <si>
-    <t>0.1927,0.0013,0.0066,0.9060</t>
-  </si>
-  <si>
-    <t>0.0111,0.0496,0.0030,0.9877</t>
-  </si>
-  <si>
-    <t>0.1821,0.0145,0.0022,0.9078</t>
-  </si>
-  <si>
-    <t>0.0027,0.0010,0.0012,0.9980</t>
-  </si>
-  <si>
-    <t>0.0020,0.0051,0.0002,0.9987</t>
-  </si>
-  <si>
-    <t>0.5686,0.0870,0.1146,0.3132</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.4339,0.1699,0.0253,0.4623</t>
+  </si>
+  <si>
+    <t>0.0189,0.0179,0.0022,0.9890</t>
+  </si>
+  <si>
+    <t>0.1154,0.2294,0.0049,0.7644</t>
+  </si>
+  <si>
+    <t>0.1063,0.0104,0.0029,0.9594</t>
+  </si>
+  <si>
+    <t>0.9793,0.0173,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9863,0.0061,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.9717,0.0214,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.9836,0.0121,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9846,0.0129,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9804,0.0156,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.9883,0.0033,0.0005,0.0022</t>
+  </si>
+  <si>
+    <t>0.9891,0.0058,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.3929,0.1732,0.5084,0.0329</t>
+  </si>
+  <si>
+    <t>0.2646,0.0164,0.8332,0.0075</t>
+  </si>
+  <si>
+    <t>0.2546,0.0629,0.7169,0.0039</t>
+  </si>
+  <si>
+    <t>0.1474,0.1608,0.6517,0.0540</t>
+  </si>
+  <si>
+    <t>0.5099,0.0423,0.5810,0.0210</t>
+  </si>
+  <si>
+    <t>0.0824,0.9344,0.0106,0.0005</t>
+  </si>
+  <si>
+    <t>0.1884,0.8557,0.0131,0.0008</t>
+  </si>
+  <si>
+    <t>0.3488,0.7294,0.0144,0.0030</t>
+  </si>
+  <si>
+    <t>0.1831,0.8901,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.0414,0.9686,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.5600,0.0153,0.2378,0.1547</t>
+  </si>
+  <si>
+    <t>0.3211,0.0402,0.6701,0.0325</t>
+  </si>
+  <si>
+    <t>0.0274,0.0066,0.9514,0.0303</t>
+  </si>
+  <si>
+    <t>0.0723,0.1177,0.7725,0.0112</t>
+  </si>
+  <si>
+    <t>0.0771,0.0077,0.9274,0.0164</t>
+  </si>
+  <si>
+    <t>0.0401,0.0024,0.9612,0.0103</t>
+  </si>
+  <si>
+    <t>0.0181,0.0031,0.9742,0.0086</t>
+  </si>
+  <si>
+    <t>0.2124,0.8484,0.0118,0.0043</t>
+  </si>
+  <si>
+    <t>0.4808,0.1787,0.4245,0.0081</t>
+  </si>
+  <si>
+    <t>0.0031,0.1778,0.9768,0.0016</t>
+  </si>
+  <si>
+    <t>0.0213,0.8363,0.3528,0.0020</t>
+  </si>
+  <si>
+    <t>0.7417,0.1824,0.0456,0.0376</t>
+  </si>
+  <si>
+    <t>0.5791,0.4195,0.0598,0.0131</t>
+  </si>
+  <si>
+    <t>0.5841,0.4862,0.0217,0.0026</t>
+  </si>
+  <si>
+    <t>0.0763,0.9200,0.0488,0.0014</t>
+  </si>
+  <si>
+    <t>0.0080,0.9264,0.1605,0.0156</t>
+  </si>
+  <si>
+    <t>0.0037,0.0082,0.9809,0.0149</t>
+  </si>
+  <si>
+    <t>0.0170,0.1115,0.9189,0.0092</t>
+  </si>
+  <si>
+    <t>0.0340,0.0155,0.9307,0.0374</t>
+  </si>
+  <si>
+    <t>0.0088,0.1377,0.9162,0.0157</t>
+  </si>
+  <si>
+    <t>0.0027,0.9738,0.1240,0.0009</t>
+  </si>
+  <si>
+    <t>0.0058,0.6552,0.7441,0.0014</t>
+  </si>
+  <si>
+    <t>0.0721,0.7773,0.0431,0.3935</t>
+  </si>
+  <si>
+    <t>0.0015,0.9755,0.0063,0.0710</t>
+  </si>
+  <si>
+    <t>0.0054,0.9590,0.2072,0.0035</t>
+  </si>
+  <si>
+    <t>0.0034,0.9599,0.0233,0.0760</t>
+  </si>
+  <si>
+    <t>0.0246,0.1127,0.9185,0.0232</t>
+  </si>
+  <si>
+    <t>0.0022,0.0723,0.9857,0.0012</t>
+  </si>
+  <si>
+    <t>0.0577,0.0637,0.8548,0.0261</t>
+  </si>
+  <si>
+    <t>0.1019,0.0213,0.8864,0.0184</t>
+  </si>
+  <si>
+    <t>0.0073,0.0084,0.9880,0.0027</t>
+  </si>
+  <si>
+    <t>0.0195,0.0430,0.9415,0.0028</t>
+  </si>
+  <si>
+    <t>0.8369,0.1685,0.0188,0.0064</t>
+  </si>
+  <si>
+    <t>0.9610,0.0111,0.0054,0.0103</t>
+  </si>
+  <si>
+    <t>0.9574,0.0204,0.0027,0.0083</t>
+  </si>
+  <si>
+    <t>0.0754,0.1244,0.8885,0.0288</t>
+  </si>
+  <si>
+    <t>0.9707,0.0121,0.0033,0.0045</t>
+  </si>
+  <si>
+    <t>0.9762,0.0195,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.9421,0.0740,0.0051,0.0014</t>
+  </si>
+  <si>
+    <t>0.0037,0.8961,0.6443,0.0052</t>
+  </si>
+  <si>
+    <t>0.0070,0.0425,0.9677,0.0117</t>
+  </si>
+  <si>
+    <t>0.0039,0.0161,0.9852,0.0035</t>
+  </si>
+  <si>
+    <t>0.0008,0.9094,0.8841,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0404,0.9827,0.0066</t>
+  </si>
+  <si>
+    <t>0.0601,0.8076,0.3060,0.0037</t>
+  </si>
+  <si>
+    <t>0.0181,0.9753,0.0097,0.0003</t>
+  </si>
+  <si>
+    <t>0.7804,0.1093,0.1543,0.0120</t>
+  </si>
+  <si>
+    <t>0.5457,0.3787,0.1820,0.0214</t>
+  </si>
+  <si>
+    <t>0.0386,0.3953,0.8662,0.0064</t>
+  </si>
+  <si>
+    <t>0.0003,0.9798,0.6815,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.8213,0.9107,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.9835,0.2695,0.0002</t>
+  </si>
+  <si>
+    <t>0.0077,0.7832,0.8679,0.0029</t>
+  </si>
+  <si>
+    <t>0.0315,0.0094,0.0044,0.9824</t>
+  </si>
+  <si>
+    <t>0.0015,0.0112,0.0018,0.9980</t>
+  </si>
+  <si>
+    <t>0.0071,0.0273,0.0010,0.9944</t>
+  </si>
+  <si>
+    <t>0.0811,0.0034,0.0053,0.9633</t>
+  </si>
+  <si>
+    <t>0.0275,0.0127,0.0043,0.9846</t>
+  </si>
+  <si>
+    <t>0.0030,0.0223,0.0019,0.9964</t>
+  </si>
+  <si>
+    <t>0.0029,0.7942,0.8754,0.0004</t>
+  </si>
+  <si>
+    <t>0.0048,0.5813,0.8920,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.8309,0.7531,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.3628,0.9775,0.0006</t>
+  </si>
+  <si>
+    <t>0.0021,0.8895,0.7538,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.8812,0.7673,0.0002</t>
+  </si>
+  <si>
+    <t>0.9808,0.0182,0.0024,0.0008</t>
+  </si>
+  <si>
+    <t>0.9824,0.0109,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9468,0.0582,0.0069,0.0018</t>
+  </si>
+  <si>
+    <t>0.9723,0.0110,0.0022,0.0046</t>
+  </si>
+  <si>
+    <t>0.9789,0.0102,0.0017,0.0024</t>
+  </si>
+  <si>
+    <t>0.9875,0.0080,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9645,0.0369,0.0035,0.0012</t>
+  </si>
+  <si>
+    <t>0.9819,0.0049,0.0014,0.0034</t>
+  </si>
+  <si>
+    <t>0.9828,0.0070,0.0013,0.0025</t>
+  </si>
+  <si>
+    <t>0.9885,0.0041,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9830,0.0124,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9891,0.0047,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9876,0.0076,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9816,0.0083,0.0011,0.0024</t>
+  </si>
+  <si>
+    <t>0.9868,0.0059,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9765,0.0144,0.0026,0.0021</t>
+  </si>
+  <si>
+    <t>0.0057,0.0055,0.9870,0.0048</t>
+  </si>
+  <si>
+    <t>0.0861,0.0140,0.9146,0.0097</t>
+  </si>
+  <si>
+    <t>0.4654,0.0198,0.0259,0.6015</t>
+  </si>
+  <si>
+    <t>0.0648,0.1421,0.7747,0.0714</t>
+  </si>
+  <si>
+    <t>0.1223,0.9059,0.0068,0.0007</t>
+  </si>
+  <si>
+    <t>0.0729,0.9352,0.0107,0.0008</t>
+  </si>
+  <si>
+    <t>0.2923,0.8140,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.3680,0.7172,0.0123,0.0043</t>
+  </si>
+  <si>
+    <t>0.0578,0.9468,0.0031,0.0010</t>
+  </si>
+  <si>
+    <t>0.0643,0.9476,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.4084,0.7137,0.0066,0.0037</t>
+  </si>
+  <si>
+    <t>0.4927,0.2045,0.4315,0.0332</t>
+  </si>
+  <si>
+    <t>0.1968,0.0488,0.8057,0.0068</t>
+  </si>
+  <si>
+    <t>0.3219,0.3137,0.3961,0.0379</t>
+  </si>
+  <si>
+    <t>0.5801,0.1667,0.3045,0.1015</t>
+  </si>
+  <si>
+    <t>0.4050,0.0601,0.0699,0.5686</t>
+  </si>
+  <si>
+    <t>0.0020,0.9881,0.0795,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.9894,0.0121,0.0042</t>
+  </si>
+  <si>
+    <t>0.0165,0.9251,0.0142,0.1085</t>
+  </si>
+  <si>
+    <t>0.0005,0.9507,0.9229,0.0001</t>
+  </si>
+  <si>
+    <t>0.1379,0.8910,0.0266,0.0006</t>
+  </si>
+  <si>
+    <t>0.6239,0.3180,0.0985,0.0043</t>
+  </si>
+  <si>
+    <t>0.3475,0.7314,0.0217,0.0029</t>
+  </si>
+  <si>
+    <t>0.9791,0.0147,0.0022,0.0016</t>
+  </si>
+  <si>
+    <t>0.9729,0.0096,0.0013,0.0051</t>
+  </si>
+  <si>
+    <t>0.9775,0.0059,0.0008,0.0055</t>
+  </si>
+  <si>
+    <t>0.9637,0.0127,0.0019,0.0087</t>
+  </si>
+  <si>
+    <t>0.9773,0.0147,0.0015,0.0023</t>
+  </si>
+  <si>
+    <t>0.8959,0.0503,0.0787,0.0050</t>
+  </si>
+  <si>
+    <t>0.9731,0.0084,0.0010,0.0055</t>
+  </si>
+  <si>
+    <t>0.9666,0.0143,0.0040,0.0052</t>
+  </si>
+  <si>
+    <t>0.0018,0.8415,0.8380,0.0007</t>
+  </si>
+  <si>
+    <t>0.0019,0.8999,0.7515,0.0003</t>
+  </si>
+  <si>
+    <t>0.0050,0.4541,0.8874,0.0008</t>
+  </si>
+  <si>
+    <t>0.0134,0.6411,0.7394,0.0040</t>
+  </si>
+  <si>
+    <t>0.6751,0.0588,0.3121,0.0595</t>
+  </si>
+  <si>
+    <t>0.2618,0.0844,0.0111,0.7481</t>
+  </si>
+  <si>
+    <t>0.4618,0.0100,0.5746,0.0526</t>
+  </si>
+  <si>
+    <t>0.4255,0.0722,0.2650,0.3642</t>
+  </si>
+  <si>
+    <t>0.1151,0.0032,0.0081,0.9445</t>
+  </si>
+  <si>
+    <t>0.0006,0.0029,0.0004,0.9994</t>
+  </si>
+  <si>
+    <t>0.0050,0.0113,0.0037,0.9945</t>
+  </si>
+  <si>
+    <t>0.0054,0.0010,0.0014,0.9968</t>
+  </si>
+  <si>
+    <t>0.0075,0.6865,0.8932,0.0042</t>
+  </si>
+  <si>
+    <t>0.8411,0.1731,0.0053,0.0061</t>
+  </si>
+  <si>
+    <t>0.7385,0.2325,0.0267,0.0261</t>
+  </si>
+  <si>
+    <t>0.9430,0.0291,0.0080,0.0092</t>
+  </si>
+  <si>
+    <t>0.6505,0.4772,0.0073,0.0017</t>
+  </si>
+  <si>
+    <t>0.9164,0.0203,0.0147,0.0378</t>
+  </si>
+  <si>
+    <t>0.0974,0.0192,0.0527,0.9148</t>
+  </si>
+  <si>
+    <t>0.9367,0.0209,0.0220,0.0143</t>
+  </si>
+  <si>
+    <t>0.0054,0.5480,0.9246,0.0038</t>
+  </si>
+  <si>
+    <t>0.6372,0.0024,0.0681,0.2392</t>
+  </si>
+  <si>
+    <t>0.9446,0.0150,0.0108,0.0161</t>
+  </si>
+  <si>
+    <t>0.2921,0.7740,0.0130,0.0085</t>
+  </si>
+  <si>
+    <t>0.7171,0.2368,0.0668,0.0305</t>
+  </si>
+  <si>
+    <t>0.8374,0.0915,0.0834,0.0095</t>
+  </si>
+  <si>
+    <t>0.3445,0.6186,0.1151,0.0425</t>
+  </si>
+  <si>
+    <t>0.7920,0.1205,0.1222,0.0063</t>
+  </si>
+  <si>
+    <t>0.3572,0.6660,0.0108,0.0281</t>
+  </si>
+  <si>
+    <t>0.9763,0.0093,0.0029,0.0036</t>
+  </si>
+  <si>
+    <t>0.9345,0.0499,0.0079,0.0049</t>
+  </si>
+  <si>
+    <t>0.9835,0.0056,0.0015,0.0024</t>
+  </si>
+  <si>
+    <t>0.9841,0.0028,0.0015,0.0045</t>
+  </si>
+  <si>
+    <t>0.9360,0.0247,0.0204,0.0110</t>
+  </si>
+  <si>
+    <t>0.9566,0.0326,0.0124,0.0027</t>
+  </si>
+  <si>
+    <t>0.9549,0.0210,0.0013,0.0075</t>
+  </si>
+  <si>
+    <t>0.9819,0.0069,0.0010,0.0026</t>
+  </si>
+  <si>
+    <t>0.2496,0.8234,0.0104,0.0027</t>
+  </si>
+  <si>
+    <t>0.5550,0.5631,0.0174,0.0012</t>
+  </si>
+  <si>
+    <t>0.3817,0.6781,0.0247,0.0027</t>
+  </si>
+  <si>
+    <t>0.3209,0.3217,0.4479,0.0114</t>
+  </si>
+  <si>
+    <t>0.9542,0.0423,0.0074,0.0014</t>
+  </si>
+  <si>
+    <t>0.8515,0.1445,0.0191,0.0042</t>
+  </si>
+  <si>
+    <t>0.9172,0.0685,0.0063,0.0067</t>
+  </si>
+  <si>
+    <t>0.8342,0.1591,0.0021,0.0110</t>
+  </si>
+  <si>
+    <t>0.0071,0.0629,0.9843,0.0003</t>
+  </si>
+  <si>
+    <t>0.9338,0.0336,0.0074,0.0137</t>
+  </si>
+  <si>
+    <t>0.0036,0.0151,0.9896,0.0003</t>
+  </si>
+  <si>
+    <t>0.0146,0.4797,0.8699,0.0026</t>
+  </si>
+  <si>
+    <t>0.0145,0.0298,0.9617,0.0052</t>
+  </si>
+  <si>
+    <t>0.0278,0.4075,0.8740,0.0045</t>
+  </si>
+  <si>
+    <t>0.0069,0.2120,0.9464,0.0037</t>
+  </si>
+  <si>
+    <t>0.0122,0.0054,0.9788,0.0020</t>
+  </si>
+  <si>
+    <t>0.0020,0.0017,0.9958,0.0009</t>
+  </si>
+  <si>
+    <t>0.0601,0.0480,0.8953,0.0080</t>
+  </si>
+  <si>
+    <t>0.0996,0.0955,0.8306,0.0040</t>
+  </si>
+  <si>
+    <t>0.4844,0.1317,0.4922,0.0406</t>
+  </si>
+  <si>
+    <t>0.5039,0.0571,0.5887,0.0084</t>
+  </si>
+  <si>
+    <t>0.0481,0.2611,0.7702,0.0021</t>
+  </si>
+  <si>
+    <t>0.4504,0.1263,0.5113,0.0220</t>
+  </si>
+  <si>
+    <t>0.5675,0.0779,0.4496,0.0257</t>
+  </si>
+  <si>
+    <t>0.2027,0.0278,0.8051,0.0092</t>
+  </si>
+  <si>
+    <t>0.4918,0.5212,0.0524,0.0039</t>
+  </si>
+  <si>
+    <t>0.7402,0.3664,0.0086,0.0017</t>
+  </si>
+  <si>
+    <t>0.7147,0.4205,0.0062,0.0017</t>
+  </si>
+  <si>
+    <t>0.9626,0.0229,0.0023,0.0039</t>
+  </si>
+  <si>
+    <t>0.8058,0.3073,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.1740,0.5536,0.3307,0.0221</t>
+  </si>
+  <si>
+    <t>0.7058,0.0452,0.2775,0.0544</t>
+  </si>
+  <si>
+    <t>0.5677,0.0979,0.1199,0.2258</t>
+  </si>
+  <si>
+    <t>0.3460,0.0182,0.7091,0.0427</t>
+  </si>
+  <si>
+    <t>0.6969,0.0489,0.2607,0.0627</t>
+  </si>
+  <si>
+    <t>0.0019,0.0355,0.9884,0.0008</t>
+  </si>
+  <si>
+    <t>0.0422,0.6915,0.4907,0.0289</t>
+  </si>
+  <si>
+    <t>0.0340,0.5318,0.7301,0.0264</t>
+  </si>
+  <si>
+    <t>0.0087,0.2164,0.9000,0.0115</t>
+  </si>
+  <si>
+    <t>0.0035,0.3119,0.9151,0.0009</t>
+  </si>
+  <si>
+    <t>0.9570,0.0132,0.0012,0.0127</t>
+  </si>
+  <si>
+    <t>0.9573,0.0369,0.0043,0.0024</t>
+  </si>
+  <si>
+    <t>0.9830,0.0075,0.0006,0.0021</t>
+  </si>
+  <si>
+    <t>0.9751,0.0212,0.0020,0.0013</t>
+  </si>
+  <si>
+    <t>0.9637,0.0311,0.0039,0.0025</t>
+  </si>
+  <si>
+    <t>0.9621,0.0266,0.0046,0.0027</t>
+  </si>
+  <si>
+    <t>0.9572,0.0029,0.0004,0.0305</t>
+  </si>
+  <si>
+    <t>0.9646,0.0270,0.0058,0.0022</t>
+  </si>
+  <si>
+    <t>0.2943,0.0407,0.7447,0.0282</t>
+  </si>
+  <si>
+    <t>0.2100,0.6143,0.1966,0.0024</t>
+  </si>
+  <si>
+    <t>0.7580,0.0168,0.1394,0.0947</t>
+  </si>
+  <si>
+    <t>0.0047,0.0860,0.9740,0.0009</t>
+  </si>
+  <si>
+    <t>0.0016,0.2965,0.9476,0.0015</t>
+  </si>
+  <si>
+    <t>0.0059,0.0536,0.9719,0.0006</t>
+  </si>
+  <si>
+    <t>0.0018,0.0188,0.9927,0.0011</t>
+  </si>
+  <si>
+    <t>0.0979,0.1420,0.7807,0.0113</t>
+  </si>
+  <si>
+    <t>0.0052,0.0218,0.9786,0.0051</t>
+  </si>
+  <si>
+    <t>0.0151,0.4048,0.7756,0.0021</t>
+  </si>
+  <si>
+    <t>0.0416,0.0230,0.9294,0.0104</t>
+  </si>
+  <si>
+    <t>0.4091,0.0482,0.6149,0.0430</t>
+  </si>
+  <si>
+    <t>0.4443,0.0592,0.5598,0.0697</t>
+  </si>
+  <si>
+    <t>0.7503,0.0204,0.2376,0.0370</t>
+  </si>
+  <si>
+    <t>0.9813,0.0091,0.0014,0.0022</t>
+  </si>
+  <si>
+    <t>0.9869,0.0088,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9798,0.0093,0.0028,0.0026</t>
+  </si>
+  <si>
+    <t>0.9588,0.0396,0.0036,0.0018</t>
+  </si>
+  <si>
+    <t>0.9524,0.0393,0.0014,0.0036</t>
+  </si>
+  <si>
+    <t>0.9614,0.0520,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.9771,0.0129,0.0005,0.0033</t>
+  </si>
+  <si>
+    <t>0.9661,0.0257,0.0015,0.0026</t>
+  </si>
+  <si>
+    <t>0.0453,0.5513,0.6269,0.0225</t>
+  </si>
+  <si>
+    <t>0.0118,0.0937,0.9622,0.0012</t>
+  </si>
+  <si>
+    <t>0.0154,0.0285,0.9600,0.0043</t>
+  </si>
+  <si>
+    <t>0.0383,0.0609,0.8653,0.0200</t>
+  </si>
+  <si>
+    <t>0.0151,0.0121,0.9693,0.0121</t>
+  </si>
+  <si>
+    <t>0.0723,0.0656,0.8708,0.0577</t>
+  </si>
+  <si>
+    <t>0.0746,0.0281,0.8144,0.1778</t>
+  </si>
+  <si>
+    <t>0.0032,0.0047,0.9765,0.0201</t>
+  </si>
+  <si>
+    <t>0.5134,0.0039,0.0051,0.6950</t>
+  </si>
+  <si>
+    <t>0.0045,0.0350,0.0023,0.9943</t>
+  </si>
+  <si>
+    <t>0.0656,0.0729,0.0043,0.9518</t>
+  </si>
+  <si>
+    <t>0.0235,0.0012,0.0006,0.9932</t>
+  </si>
+  <si>
+    <t>0.0071,0.0027,0.0007,0.9965</t>
+  </si>
+  <si>
+    <t>0.5462,0.0266,0.2048,0.3137</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2136,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2539,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2567,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2584,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4121,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4233,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4513,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4541,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>262</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4877,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5339,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
